--- a/public/templates/Beverly_Freight_Inc_template.xlsx
+++ b/public/templates/Beverly_Freight_Inc_template.xlsx
@@ -2295,6 +2295,7 @@
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
     </row>
+    <row r="70" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="C13:D13"/>
